--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C17461-8E92-4C91-93F9-8A429BD7745E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE58A19D-6573-4166-883D-8F1F315722F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21255" yWindow="1035" windowWidth="20055" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="585" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>Name</t>
   </si>
@@ -113,6 +113,81 @@
   </si>
   <si>
     <t>로셸</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>oveSpeed</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ttackDamage</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ttackCoolDown</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -233,7 +308,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -257,6 +332,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -671,7 +747,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
@@ -681,7 +757,7 @@
     <col min="5" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -693,7 +769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="12.75">
+    <row r="2" spans="1:9" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -706,8 +782,21 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="E2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -720,8 +809,21 @@
       <c r="D3" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="E3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -734,8 +836,20 @@
       <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="E4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="3">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -748,8 +862,20 @@
       <c r="D5" s="12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="E5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -762,8 +888,20 @@
       <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="E6" s="3">
+        <v>800</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3">
+        <v>8</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -776,48 +914,60 @@
       <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="E7" s="3">
+        <v>800</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7</v>
+      </c>
+      <c r="G7" s="3">
+        <v>8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE58A19D-6573-4166-883D-8F1F315722F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9863E75-51AE-4DA5-8D8B-70DEDB78D125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="585" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -157,36 +157,6 @@
         <family val="2"/>
       </rPr>
       <t>oveSpeed</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ttackDamage</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ttackCoolDown</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -788,12 +758,8 @@
       <c r="F2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>25</v>
-      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
@@ -815,12 +781,8 @@
       <c r="F3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
@@ -842,12 +804,6 @@
       <c r="F4" s="3">
         <v>5</v>
       </c>
-      <c r="G4" s="3">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -868,12 +824,6 @@
       <c r="F5" s="3">
         <v>5</v>
       </c>
-      <c r="G5" s="3">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
@@ -894,12 +844,6 @@
       <c r="F6" s="3">
         <v>7</v>
       </c>
-      <c r="G6" s="3">
-        <v>8</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -919,12 +863,6 @@
       </c>
       <c r="F7" s="3">
         <v>7</v>
-      </c>
-      <c r="G7" s="3">
-        <v>8</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9863E75-51AE-4DA5-8D8B-70DEDB78D125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28934CAA-AEDD-4922-B463-A7E199C9A47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="795" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -158,6 +158,18 @@
       </rPr>
       <t>oveSpeed</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_instance_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -717,17 +729,17 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="40" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="12.5703125" style="3"/>
+    <col min="3" max="4" width="22.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -735,11 +747,12 @@
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="12.75">
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -750,19 +763,22 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>25</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -772,20 +788,23 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -795,17 +814,20 @@
       <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>1000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -815,17 +837,20 @@
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>1000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -835,17 +860,20 @@
       <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>800</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -855,169 +883,200 @@
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>800</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28934CAA-AEDD-4922-B463-A7E199C9A47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C6488B-AF0E-4B95-8C95-3B2C7C1E54EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="795" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -166,6 +166,10 @@
   </si>
   <si>
     <t>SkillId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_projectile_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -815,7 +819,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
@@ -838,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>18</v>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C6488B-AF0E-4B95-8C95-3B2C7C1E54EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFBFB48-D28A-4511-99BA-A3C168F06579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -174,6 +174,10 @@
   </si>
   <si>
     <t>skill_instance_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -887,8 +891,8 @@
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>20</v>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFBFB48-D28A-4511-99BA-A3C168F06579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256DE3F6-D29E-4B89-A44A-75A24FD8E12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="720" windowWidth="22275" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -178,6 +178,10 @@
   </si>
   <si>
     <t>skill_area_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_03</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -845,8 +849,8 @@
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>18</v>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256DE3F6-D29E-4B89-A44A-75A24FD8E12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA318DB-4EF8-45A9-A171-18AE73E33CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="720" windowWidth="22275" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>skill_area_03</t>
+    <t>skill_instance_02</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -849,7 +849,7 @@
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="12" t="s">

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA318DB-4EF8-45A9-A171-18AE73E33CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CF6AA6-D524-40D3-AE51-090C9AFDAA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -177,12 +177,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>skill_area_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>skill_instance_02</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_02</t>
   </si>
 </sst>
 </file>
@@ -850,7 +849,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>18</v>
@@ -896,7 +895,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>20</v>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CF6AA6-D524-40D3-AE51-090C9AFDAA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87813385-67DC-47DB-A301-287D5EB9C27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -878,7 +878,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="3">
-        <v>800</v>
+        <v>10000000</v>
       </c>
       <c r="G6" s="3">
         <v>7</v>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87813385-67DC-47DB-A301-287D5EB9C27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B7E2B-964C-470E-8335-287193B8D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,8 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>skill_area_02</t>
+    <t>skill_area_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B7E2B-964C-470E-8335-287193B8D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A68EBB1-0AF1-450D-B928-01B5AFD73DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -65,22 +65,6 @@
   </si>
   <si>
     <t>Player_Unit_FeMale_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>남자캐릭터 1번</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>남자캐릭터 2번</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여자캐릭터 1번</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여자캐릭터 2번</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -182,6 +166,41 @@
   </si>
   <si>
     <t>skill_area_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 근접 공격으로 적을 휩쓴다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 모아 강력한 에너지를 발사한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 날려 적에게 데미지를 준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 지대를 소환하여 주변 적들에게 피해를 입힌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>conPath</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -741,17 +760,18 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="4" width="22.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="12.5703125" style="3"/>
+    <col min="3" max="3" width="55.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="40" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -763,8 +783,9 @@
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="12.75">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -775,22 +796,25 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>25</v>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -801,162 +825,169 @@
         <v>4</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12"/>
+      <c r="G4" s="3">
         <v>1000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="F5" s="12"/>
+      <c r="G5" s="3">
         <v>1000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="F6" s="12"/>
+      <c r="G6" s="3">
         <v>10000000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="F7" s="12"/>
+      <c r="G7" s="3">
         <v>800</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A68EBB1-0AF1-450D-B928-01B5AFD73DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAB732F-1E42-4247-8141-E7BCB5F49CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="735" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -203,12 +203,28 @@
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Icon/PlayerUnit_Icon/Jade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/PlayerUnit_Icon/Alice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/PlayerUnit_Icon/Chris</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/PlayerUnit_Icon/Rochelle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -246,6 +262,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -321,7 +344,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -346,6 +369,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -859,7 +883,9 @@
       <c r="E4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="G4" s="3">
         <v>1000</v>
       </c>
@@ -883,7 +909,9 @@
       <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="G5" s="3">
         <v>1000</v>
       </c>
@@ -907,7 +935,9 @@
       <c r="E6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="G6" s="3">
         <v>10000000</v>
       </c>
@@ -931,7 +961,9 @@
       <c r="E7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="G7" s="3">
         <v>800</v>
       </c>

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAB732F-1E42-4247-8141-E7BCB5F49CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9528C8EF-22F2-4DC2-BF7B-DE962849C7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="735" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H4" s="3">
         <v>5</v>
@@ -913,7 +913,7 @@
         <v>38</v>
       </c>
       <c r="G5" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H5" s="3">
         <v>5</v>
@@ -939,10 +939,10 @@
         <v>37</v>
       </c>
       <c r="G6" s="3">
-        <v>10000000</v>
+        <v>500</v>
       </c>
       <c r="H6" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
@@ -965,10 +965,10 @@
         <v>39</v>
       </c>
       <c r="G7" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H7" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/PlayerUnit.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9528C8EF-22F2-4DC2-BF7B-DE962849C7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E4FC46-B719-444D-8AC3-C97E6CA2FF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="720" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="720" windowWidth="27315" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="3">
-        <v>500</v>
+        <v>100000</v>
       </c>
       <c r="H4" s="3">
         <v>5</v>
@@ -939,7 +939,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="3">
-        <v>500</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
